--- a/html/tech_html_demo/res/モック画面設計.xlsx
+++ b/html/tech_html_demo/res/モック画面設計.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saisk\git0620\tech_html_demo\tech_html_demo\res\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tech\git20220205\tech\html\tech_html_demo\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123AE4E1-9E8A-437C-91C6-9661C67787F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11616" activeTab="4"/>
+    <workbookView minimized="1" xWindow="2660" yWindow="2660" windowWidth="19200" windowHeight="11260" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="授業内容" sheetId="4" r:id="rId1"/>
@@ -17,6 +18,7 @@
     <sheet name="検索一覧" sheetId="3" r:id="rId3"/>
     <sheet name="新規作成" sheetId="2" r:id="rId4"/>
     <sheet name="開発流れ" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="104">
   <si>
     <r>
       <t>学</t>
@@ -37,7 +39,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -54,7 +56,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -71,7 +73,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -92,7 +94,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -109,7 +111,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -120,7 +122,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -180,7 +182,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -197,7 +199,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -222,7 +224,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -232,7 +234,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -249,7 +251,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -259,7 +261,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -280,7 +282,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -308,7 +310,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -319,7 +321,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -332,7 +334,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -343,7 +345,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -367,7 +369,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -388,7 +390,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -405,7 +407,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -422,7 +424,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -447,7 +449,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -458,7 +460,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -468,7 +470,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -485,7 +487,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -504,7 +506,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -524,7 +526,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -535,7 +537,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -551,7 +553,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -562,7 +564,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -578,7 +580,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -595,7 +597,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -606,7 +608,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -617,7 +619,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -638,7 +640,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -651,7 +653,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -662,7 +664,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -672,7 +674,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -689,7 +691,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -700,7 +702,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -721,7 +723,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -750,7 +752,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -767,7 +769,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -787,7 +789,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -808,7 +810,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -824,7 +826,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -841,7 +843,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -890,7 +892,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -907,7 +909,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -924,7 +926,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -950,22 +952,126 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>何のために、HTMLを勉強する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HTML，CSS·，JSP，JS，JQUERYの区別</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自宅勉強</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宿題説明</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSS様式</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DOM,JQUERY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DEBUG</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現場の経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PJ流れ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>其の他</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NO.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>名前</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>給料</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>誕生日</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>住所</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>０１</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>田中太郎</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>東京都千代田区大手町１－１－２</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>田中次郎</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>田中三郎</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>東京都岩本町１－１－２</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>北海道３２０１</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>head</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>data</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>０２</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>０３</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="Yu Gothic"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -973,13 +1079,20 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -992,8 +1105,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1001,17 +1120,114 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1046,7 +1262,7 @@
         <xdr:cNvPr id="7" name="图片 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C637A940-97D5-4B40-9C30-FBE990DDC519}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C637A940-97D5-4B40-9C30-FBE990DDC519}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1090,7 +1306,7 @@
         <xdr:cNvPr id="8" name="图片 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{291077C9-1A31-4A54-8D7D-5375DCCC7F91}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{291077C9-1A31-4A54-8D7D-5375DCCC7F91}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1139,7 +1355,7 @@
         <xdr:cNvPr id="9" name="图片 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FAE5194-7B86-44B2-BA4E-60F8440D08A7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FAE5194-7B86-44B2-BA4E-60F8440D08A7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1183,7 +1399,7 @@
         <xdr:cNvPr id="19" name="图片 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47E67154-AAD0-4146-AAA0-F503D06B9807}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47E67154-AAD0-4146-AAA0-F503D06B9807}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1227,7 +1443,7 @@
         <xdr:cNvPr id="20" name="图片 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30388678-BB23-4B09-AA6A-94C9C51A54E5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30388678-BB23-4B09-AA6A-94C9C51A54E5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1276,7 +1492,7 @@
         <xdr:cNvPr id="8" name="图片 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65B117D7-DF5E-4E97-B192-6E8464F1BA2D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65B117D7-DF5E-4E97-B192-6E8464F1BA2D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1320,7 +1536,7 @@
         <xdr:cNvPr id="9" name="图片 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8E19347-6010-4262-A40F-175C7ECA9F19}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8E19347-6010-4262-A40F-175C7ECA9F19}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1611,101 +1827,140 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="F2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="F3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="F4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
+      <c r="F5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
+      <c r="F7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
+      <c r="F8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
+      <c r="F9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
+      <c r="F12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:2">
+      <c r="F13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:2">
+      <c r="F14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="2:2">
+      <c r="F17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="2:2">
+      <c r="F18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>7</v>
+      </c>
+      <c r="F19" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1716,9 +1971,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1728,9 +1983,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1740,19 +1995,19 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B3:B42"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
+    <col min="1" max="1" width="3.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:2">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="42" spans="2:2">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>77</v>
       </c>
@@ -1765,17 +2020,17 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A2:M63"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.4140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1789,70 +2044,70 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E12" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D14" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -1866,17 +2121,17 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
         <v>38</v>
       </c>
@@ -1884,7 +2139,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
         <v>39</v>
       </c>
@@ -1892,7 +2147,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D25" s="1" t="s">
         <v>40</v>
       </c>
@@ -1900,12 +2155,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F26" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -1916,7 +2171,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
         <v>38</v>
       </c>
@@ -1924,7 +2179,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
         <v>39</v>
       </c>
@@ -1932,7 +2187,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D33" s="1" t="s">
         <v>42</v>
       </c>
@@ -1940,7 +2195,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D34" s="1" t="s">
         <v>47</v>
       </c>
@@ -1948,7 +2203,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D35" s="1" t="s">
         <v>48</v>
       </c>
@@ -1956,7 +2211,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D36" s="1" t="s">
         <v>51</v>
       </c>
@@ -1964,7 +2219,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D37" s="1" t="s">
         <v>52</v>
       </c>
@@ -1972,7 +2227,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>4</v>
       </c>
@@ -1983,7 +2238,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D39" s="1" t="s">
         <v>50</v>
       </c>
@@ -1997,7 +2252,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L40" t="s">
         <v>71</v>
       </c>
@@ -2005,7 +2260,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>5</v>
       </c>
@@ -2022,27 +2277,27 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>6</v>
       </c>
@@ -2054,12 +2309,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D47" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D48" s="1" t="s">
         <v>61</v>
       </c>
@@ -2067,7 +2322,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>7</v>
       </c>
@@ -2078,7 +2333,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D51" s="1" t="s">
         <v>59</v>
       </c>
@@ -2086,7 +2341,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D52" s="1" t="s">
         <v>61</v>
       </c>
@@ -2094,7 +2349,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>8</v>
       </c>
@@ -2105,7 +2360,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B55" s="1"/>
       <c r="D55" t="s">
         <v>60</v>
@@ -2114,7 +2369,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>9</v>
       </c>
@@ -2122,12 +2377,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D58" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>10</v>
       </c>
@@ -2138,12 +2393,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
         <v>64</v>
       </c>
@@ -2153,4 +2408,101 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738E7EEB-8F2E-4E81-B6AC-24E79B1BBBFD}">
+  <dimension ref="B3:G7"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.08203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:7" ht="14.5" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="9">
+        <v>37288</v>
+      </c>
+      <c r="F5" s="3">
+        <v>300001</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="9">
+        <v>37289</v>
+      </c>
+      <c r="F6" s="3">
+        <v>300002</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="9">
+        <v>37290</v>
+      </c>
+      <c r="F7" s="3">
+        <v>5000001</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>